--- a/research/traditional_assets/database/data/australia/australia_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_computers_peripherals.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.5595</v>
+        <v>-0.134</v>
       </c>
       <c r="G2">
-        <v>-0.3466516419832582</v>
+        <v>-0.5154099631711572</v>
       </c>
       <c r="H2">
-        <v>-1.135962652929813</v>
+        <v>-0.8223492924985462</v>
       </c>
       <c r="I2">
-        <v>-1.159047005795235</v>
+        <v>-0.8679007559604575</v>
       </c>
       <c r="J2">
-        <v>-1.159047005795235</v>
+        <v>-0.8679007559604575</v>
       </c>
       <c r="K2">
-        <v>-34.78</v>
+        <v>-16.97</v>
       </c>
       <c r="L2">
-        <v>-1.119768190598841</v>
+        <v>-0.8223492924985462</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.631</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01753752084491384</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.03718326458456099</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,76 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.631</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>52.119</v>
+        <v>17.225</v>
       </c>
       <c r="V2">
-        <v>0.1192436167292029</v>
+        <v>0.4787381878821567</v>
       </c>
       <c r="W2">
-        <v>-1.025960539979232</v>
+        <v>-0.4313538886393065</v>
       </c>
       <c r="X2">
-        <v>0.113971504962462</v>
+        <v>0.1004833941657933</v>
       </c>
       <c r="Y2">
-        <v>-1.139932044941693</v>
+        <v>-0.5318372828050999</v>
       </c>
       <c r="Z2">
-        <v>2.182712579058327</v>
+        <v>0.891442394919867</v>
       </c>
       <c r="AA2">
-        <v>-1.943986820428336</v>
+        <v>-2.32442367990324</v>
       </c>
       <c r="AB2">
-        <v>0.109869430234056</v>
+        <v>0.09427105736918917</v>
       </c>
       <c r="AC2">
-        <v>-2.05505087892511</v>
+        <v>-2.419033920564278</v>
       </c>
       <c r="AD2">
-        <v>4.31</v>
+        <v>3.824</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.31</v>
+        <v>3.824</v>
       </c>
       <c r="AG2">
-        <v>-47.809</v>
+        <v>-13.401</v>
       </c>
       <c r="AH2">
-        <v>0.009764607263417839</v>
+        <v>0.09607074665862726</v>
       </c>
       <c r="AI2">
-        <v>0.05412532964962954</v>
+        <v>0.1092134574741532</v>
       </c>
       <c r="AJ2">
-        <v>-0.1228167523396297</v>
+        <v>-0.5935160990300723</v>
       </c>
       <c r="AK2">
-        <v>-1.737813965322962</v>
+        <v>-0.7533307099893193</v>
       </c>
       <c r="AL2">
-        <v>1.674</v>
+        <v>0.457</v>
       </c>
       <c r="AM2">
-        <v>1.671</v>
+        <v>0.1729999999999999</v>
       </c>
       <c r="AN2">
-        <v>-0.1233437312194145</v>
+        <v>-0.2265402843601896</v>
       </c>
       <c r="AO2">
-        <v>-21.50537634408602</v>
+        <v>-39.19037199124727</v>
       </c>
       <c r="AP2">
-        <v>1.368199639412758</v>
+        <v>0.793898104265403</v>
       </c>
       <c r="AQ2">
-        <v>-21.54398563734291</v>
+        <v>-103.5260115606937</v>
       </c>
     </row>
     <row r="3">
@@ -716,31 +719,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.01072243346007604</v>
+        <v>-0.08906250000000003</v>
       </c>
       <c r="H3">
-        <v>-0.02102661596958175</v>
+        <v>-0.2203125</v>
       </c>
       <c r="I3">
-        <v>-0.0220532319391635</v>
+        <v>-0.2260416666666667</v>
       </c>
       <c r="J3">
-        <v>-0.0220532319391635</v>
+        <v>-0.2260416666666667</v>
       </c>
       <c r="K3">
-        <v>-1.4</v>
+        <v>-3.71</v>
       </c>
       <c r="L3">
-        <v>-0.0532319391634981</v>
+        <v>-0.1932291666666667</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.631</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.05535087719298246</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.1700808625336927</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,76 +755,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.631</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3">
-        <v>0.7476635514018692</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="W3">
-        <v>-4.5016077170418</v>
+        <v>-0.1174050632911392</v>
       </c>
       <c r="X3">
-        <v>0.113971504962462</v>
+        <v>0.100137378257696</v>
       </c>
       <c r="Y3">
-        <v>-4.615579222004262</v>
+        <v>-0.2175424415488353</v>
       </c>
       <c r="Z3">
-        <v>6.623016872324353</v>
+        <v>1.140819964349376</v>
       </c>
       <c r="AA3">
-        <v>-0.1460589272223621</v>
+        <v>-0.2578728461081403</v>
       </c>
       <c r="AB3">
-        <v>0.109869430234056</v>
+        <v>0.09431703249303551</v>
       </c>
       <c r="AC3">
-        <v>-0.2559283574564181</v>
+        <v>-0.3521898786011758</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AG3">
-        <v>-14.77</v>
+        <v>-13.87</v>
       </c>
       <c r="AH3">
-        <v>0.05435262925320371</v>
+        <v>0.09018355945730246</v>
       </c>
       <c r="AI3">
-        <v>0.03746573256168139</v>
+        <v>0.04089757509952949</v>
       </c>
       <c r="AJ3">
-        <v>-2.227752639517345</v>
+        <v>5.615384615384614</v>
       </c>
       <c r="AK3">
-        <v>-0.8775995246583481</v>
+        <v>-1.098178939034046</v>
       </c>
       <c r="AL3">
-        <v>1.51</v>
+        <v>0.057</v>
       </c>
       <c r="AM3">
-        <v>1.508</v>
+        <v>-0.214</v>
       </c>
       <c r="AN3">
-        <v>-2.224231464737794</v>
+        <v>-0.2671394799054373</v>
       </c>
       <c r="AO3">
-        <v>-0.3841059602649006</v>
+        <v>-76.14035087719297</v>
       </c>
       <c r="AP3">
-        <v>26.70886075949367</v>
+        <v>3.278959810874704</v>
       </c>
       <c r="AQ3">
-        <v>-0.3846153846153846</v>
+        <v>20.2803738317757</v>
       </c>
     </row>
     <row r="4">
@@ -840,26 +846,23 @@
           <t>Computers/Peripherals</t>
         </is>
       </c>
-      <c r="D4">
-        <v>1.025</v>
-      </c>
       <c r="G4">
-        <v>-1.085714285714286</v>
+        <v>-15.95890410958904</v>
       </c>
       <c r="H4">
-        <v>-1.576190476190476</v>
+        <v>-22.94520547945206</v>
       </c>
       <c r="I4">
-        <v>-1.971428571428571</v>
+        <v>-28.28767123287671</v>
       </c>
       <c r="J4">
-        <v>-1.971428571428571</v>
+        <v>-28.28767123287671</v>
       </c>
       <c r="K4">
-        <v>-3.4</v>
+        <v>-3.57</v>
       </c>
       <c r="L4">
-        <v>-1.619047619047619</v>
+        <v>-24.45205479452055</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,73 +886,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.15</v>
+        <v>0.652</v>
       </c>
       <c r="V4">
-        <v>0.2956298200514139</v>
+        <v>0.1720316622691293</v>
       </c>
       <c r="W4">
-        <v>-0.5492730210016155</v>
+        <v>-0.7453027139874738</v>
       </c>
       <c r="X4">
-        <v>0.1168377524249996</v>
+        <v>0.1008294100738906</v>
       </c>
       <c r="Y4">
-        <v>-0.6661107734266151</v>
+        <v>-0.8461321240613644</v>
       </c>
       <c r="Z4">
-        <v>0.3830718715797155</v>
+        <v>0.03574926542605289</v>
       </c>
       <c r="AA4">
-        <v>-0.7551988325428675</v>
+        <v>-1.01126346718903</v>
       </c>
       <c r="AB4">
-        <v>0.1090848862328676</v>
+        <v>0.09422508224534282</v>
       </c>
       <c r="AC4">
-        <v>-0.8642837187757351</v>
+        <v>-1.105488549434373</v>
       </c>
       <c r="AD4">
-        <v>0.444</v>
+        <v>0.441</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.444</v>
+        <v>0.441</v>
       </c>
       <c r="AG4">
-        <v>-0.706</v>
+        <v>-0.211</v>
       </c>
       <c r="AH4">
-        <v>0.1024457775726811</v>
+        <v>0.1042306783266367</v>
       </c>
       <c r="AI4">
-        <v>0.08482995796713795</v>
+        <v>0.1340018231540565</v>
       </c>
       <c r="AJ4">
-        <v>-0.2217336683417085</v>
+        <v>-0.05895501536742107</v>
       </c>
       <c r="AK4">
-        <v>-0.172869735553379</v>
+        <v>-0.0799545282303903</v>
       </c>
       <c r="AL4">
         <v>0.028</v>
       </c>
       <c r="AM4">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="AN4">
-        <v>-0.1341389728096677</v>
+        <v>-0.1316417910447761</v>
       </c>
       <c r="AO4">
-        <v>-147.8571428571428</v>
+        <v>-147.5</v>
       </c>
       <c r="AP4">
-        <v>0.2132930513595166</v>
+        <v>0.06298507462686567</v>
       </c>
       <c r="AQ4">
-        <v>-147.8571428571428</v>
+        <v>-165.2</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AdvanceTC Limited (OTCPK:ATCL.F)</t>
+          <t>Nuheara Limited (ASX:NUH)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -968,8 +971,26 @@
           <t>Computers/Peripherals</t>
         </is>
       </c>
+      <c r="D5">
+        <v>-0.134</v>
+      </c>
+      <c r="G5">
+        <v>-4.155038759689922</v>
+      </c>
+      <c r="H5">
+        <v>-6.201550387596899</v>
+      </c>
+      <c r="I5">
+        <v>-6.302325581395349</v>
+      </c>
+      <c r="J5">
+        <v>-6.302325581395349</v>
+      </c>
       <c r="K5">
-        <v>-1</v>
+        <v>-8.4</v>
+      </c>
+      <c r="L5">
+        <v>-6.511627906976744</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -993,67 +1014,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.064</v>
+        <v>1.54</v>
       </c>
       <c r="V5">
-        <v>0.009566517189835574</v>
+        <v>0.08508287292817679</v>
       </c>
       <c r="W5">
-        <v>6.134969325153374</v>
+        <v>-5.714285714285714</v>
       </c>
       <c r="X5">
-        <v>0.111064058496774</v>
+        <v>0.0999729554530846</v>
       </c>
       <c r="Y5">
-        <v>6.0239052666566</v>
+        <v>-5.814258669738799</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.5771812080536913</v>
       </c>
       <c r="AA5">
-        <v>-1.943986820428336</v>
+        <v>-3.63758389261745</v>
       </c>
       <c r="AB5">
-        <v>0.111064058496774</v>
+        <v>0.09499539907673214</v>
       </c>
       <c r="AC5">
-        <v>-2.05505087892511</v>
+        <v>-3.732579291694182</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG5">
-        <v>-0.064</v>
+        <v>0.1799999999999999</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.08678102926337034</v>
       </c>
       <c r="AI5">
-        <v>-0</v>
+        <v>0.3359375</v>
       </c>
       <c r="AJ5">
-        <v>-0.009658919408391186</v>
+        <v>0.009846827133479208</v>
       </c>
       <c r="AK5">
-        <v>0.0545144804088586</v>
+        <v>0.05027932960893853</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="AN5">
-        <v>-0</v>
+        <v>-0.215</v>
+      </c>
+      <c r="AO5">
+        <v>-23.42939481268012</v>
       </c>
       <c r="AP5">
-        <v>0.05423728813559323</v>
+        <v>-0.02249999999999999</v>
+      </c>
+      <c r="AQ5">
+        <v>-24.1246290801187</v>
       </c>
     </row>
     <row r="6">
@@ -1064,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nuheara Limited (ASX:NUH)</t>
+          <t>AdvanceTC Limited (OTCPK:ATCL.F)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1072,26 +1099,8 @@
           <t>Computers/Peripherals</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.094</v>
-      </c>
-      <c r="G6">
-        <v>-1.507518796992481</v>
-      </c>
-      <c r="H6">
-        <v>-4.135338345864661</v>
-      </c>
-      <c r="I6">
-        <v>-4.210526315789473</v>
-      </c>
-      <c r="J6">
-        <v>-4.210526315789473</v>
-      </c>
       <c r="K6">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="L6">
-        <v>-3.714285714285714</v>
+        <v>-1.29</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1115,171 +1124,64 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.305</v>
+        <v>0.033</v>
       </c>
       <c r="V6">
-        <v>0.01418604651162791</v>
+        <v>0.01226765799256506</v>
       </c>
       <c r="W6">
-        <v>-1.025960539979232</v>
+        <v>2.6875</v>
       </c>
       <c r="X6">
-        <v>0.1165930992515272</v>
+        <v>0.1041129987747405</v>
       </c>
       <c r="Y6">
-        <v>-1.142553639230759</v>
-      </c>
-      <c r="Z6">
-        <v>0.6378896882494004</v>
-      </c>
-      <c r="AA6">
-        <v>-2.685851318944843</v>
+        <v>2.58338700122526</v>
       </c>
       <c r="AB6">
-        <v>0.1091604877948777</v>
-      </c>
-      <c r="AC6">
-        <v>-2.795011806739721</v>
+        <v>0.09309145861124786</v>
       </c>
       <c r="AD6">
-        <v>2.35</v>
+        <v>0.533</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.35</v>
+        <v>0.533</v>
       </c>
       <c r="AG6">
-        <v>2.045</v>
+        <v>0.5</v>
       </c>
       <c r="AH6">
-        <v>0.09853249475890985</v>
+        <v>0.1653738752714862</v>
       </c>
       <c r="AI6">
-        <v>0.5233853006681515</v>
+        <v>-0.5189873417721519</v>
       </c>
       <c r="AJ6">
-        <v>0.08685495858993415</v>
+        <v>0.1567398119122257</v>
       </c>
       <c r="AK6">
-        <v>0.4886499402628434</v>
+        <v>-0.4716981132075471</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="AM6">
-        <v>-0.001</v>
+        <v>0.025</v>
       </c>
       <c r="AN6">
-        <v>-0.2136363636363637</v>
+        <v>-0.41</v>
+      </c>
+      <c r="AO6">
+        <v>-52.4</v>
       </c>
       <c r="AP6">
-        <v>-0.1859090909090909</v>
+        <v>-0.3846153846153846</v>
       </c>
       <c r="AQ6">
-        <v>11200</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Weebit Nano Limited (ASX:WBT)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Computers/Peripherals</t>
-        </is>
-      </c>
-      <c r="K7">
-        <v>-19.1</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>34.6</v>
-      </c>
-      <c r="V7">
-        <v>0.09019812304483837</v>
-      </c>
-      <c r="W7">
-        <v>-1.20125786163522</v>
-      </c>
-      <c r="X7">
-        <v>0.111101772950661</v>
-      </c>
-      <c r="Y7">
-        <v>-1.312359634585881</v>
-      </c>
-      <c r="AB7">
-        <v>0.1110496654315958</v>
-      </c>
-      <c r="AD7">
-        <v>0.286</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0.286</v>
-      </c>
-      <c r="AG7">
-        <v>-34.314</v>
-      </c>
-      <c r="AH7">
-        <v>0.0007450128423542405</v>
-      </c>
-      <c r="AI7">
-        <v>0.007489655894830566</v>
-      </c>
-      <c r="AJ7">
-        <v>-0.09824041043729208</v>
-      </c>
-      <c r="AK7">
-        <v>-9.568878973786953</v>
-      </c>
-      <c r="AL7">
-        <v>0.136</v>
-      </c>
-      <c r="AM7">
-        <v>0.136</v>
-      </c>
-      <c r="AN7">
-        <v>-0.01513227513227513</v>
-      </c>
-      <c r="AO7">
-        <v>-138.9705882352941</v>
-      </c>
-      <c r="AP7">
-        <v>1.815555555555556</v>
-      </c>
-      <c r="AQ7">
-        <v>-138.9705882352941</v>
+        <v>-52.4</v>
       </c>
     </row>
   </sheetData>
